--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/音频_BGM配置表_Audio_BgmConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/音频_BGM配置表_Audio_BgmConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="44">
   <si>
     <t>BGM行ID</t>
   </si>
@@ -112,7 +112,25 @@
     <t>Dig</t>
   </si>
   <si>
-    <t>BGM_Dig_Ashen Plot</t>
+    <t>BGM_Dig_Mossed Hollow Loop_1</t>
+  </si>
+  <si>
+    <t>Bgm_Dig_02</t>
+  </si>
+  <si>
+    <t>BGM_Dig_Mossed Hollow Loop_2</t>
+  </si>
+  <si>
+    <t>Bgm_Dig_03</t>
+  </si>
+  <si>
+    <t>BGM_Dig_Hollow Graves_1</t>
+  </si>
+  <si>
+    <t>Bgm_Dig_04</t>
+  </si>
+  <si>
+    <t>BGM_Dig_Hollow Graves_2</t>
   </si>
   <si>
     <t>Bgm_Combat_01</t>
@@ -311,12 +329,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -637,7 +661,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -661,16 +685,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -679,90 +703,93 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1298,7 +1325,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="19.375" customWidth="1"/>
@@ -1346,23 +1373,23 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+    <row r="3" s="1" customFormat="1" spans="1:6">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1431,10 +1458,10 @@
         <v>27</v>
       </c>
       <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
         <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
       </c>
       <c r="D7" t="s">
         <v>21</v>
@@ -1448,13 +1475,13 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
         <v>30</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
       </c>
       <c r="D8" t="s">
         <v>21</v>
@@ -1468,13 +1495,13 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
         <v>32</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
       </c>
       <c r="D9" t="s">
         <v>21</v>
@@ -1488,10 +1515,10 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
         <v>34</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
       </c>
       <c r="C10" t="s">
         <v>35</v>
@@ -1511,7 +1538,7 @@
         <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
         <v>37</v>
@@ -1523,6 +1550,66 @@
         <v>21</v>
       </c>
       <c r="F11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" t="s">
         <v>21</v>
       </c>
     </row>
